--- a/figures_n_tables/tables/uea-results.xlsx
+++ b/figures_n_tables/tables/uea-results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yoom618/Library/Mobile Documents/com~apple~CloudDocs/00-Paper/06-TSC/논문 작성/_table/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yoom618/Library/Mobile Documents/com~apple~CloudDocs/00-Paper/06-TSC/논문 작성/_figures and tables/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{362C1622-5ECE-CD43-8A5A-B15FDD5C9E16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1254CE8-A1F5-F840-8E69-7523F9B68D13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15120" yWindow="760" windowWidth="15120" windowHeight="18880" xr2:uid="{BC76D622-9BC0-A344-B0B3-54E11F39A12E}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="15120" windowHeight="18980" xr2:uid="{BC76D622-9BC0-A344-B0B3-54E11F39A12E}"/>
   </bookViews>
   <sheets>
     <sheet name="UEA30 (colored)" sheetId="5" r:id="rId1"/>
@@ -901,7 +901,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -980,20 +980,14 @@
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4598,41 +4592,41 @@
   </cols>
   <sheetData>
     <row r="4" spans="1:22" ht="43" customHeight="1">
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26" t="s">
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="H4" s="26"/>
-      <c r="I4" s="26"/>
-      <c r="J4" s="26" t="s">
+      <c r="H4" s="27"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="K4" s="26"/>
-      <c r="L4" s="27" t="s">
+      <c r="K4" s="27"/>
+      <c r="L4" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="M4" s="27"/>
-      <c r="N4" s="26" t="s">
+      <c r="M4" s="28"/>
+      <c r="N4" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="O4" s="26"/>
-      <c r="P4" s="26"/>
-      <c r="Q4" s="26"/>
-      <c r="R4" s="26"/>
-      <c r="S4" s="26"/>
+      <c r="O4" s="27"/>
+      <c r="P4" s="27"/>
+      <c r="Q4" s="27"/>
+      <c r="R4" s="27"/>
+      <c r="S4" s="27"/>
       <c r="T4" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="U4" s="26" t="s">
+      <c r="U4" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="V4" s="26"/>
+      <c r="V4" s="27"/>
     </row>
     <row r="5" spans="1:22">
       <c r="A5" t="s">
@@ -4965,13 +4959,13 @@
         <v>78.048780487804876</v>
       </c>
       <c r="T9" s="3">
-        <v>80.487804878048792</v>
+        <v>80.487804878048806</v>
       </c>
       <c r="U9" s="2">
         <v>78.536585365853668</v>
       </c>
-      <c r="V9" s="2">
-        <v>80</v>
+      <c r="V9" s="3">
+        <v>80.487804878048806</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -6191,7 +6185,7 @@
       <c r="T27" s="2">
         <v>67.179999999999993</v>
       </c>
-      <c r="U27" s="30">
+      <c r="U27" s="26">
         <v>68.244</v>
       </c>
       <c r="V27" s="2">
@@ -6828,7 +6822,7 @@
       </c>
       <c r="V36" s="4">
         <f t="shared" si="0"/>
-        <v>78.778660895649992</v>
+        <v>78.827441383454868</v>
       </c>
     </row>
     <row r="37" spans="1:22">
@@ -6907,7 +6901,7 @@
         <f t="shared" si="1"/>
         <v>74.797352581492476</v>
       </c>
-      <c r="T37" s="29">
+      <c r="T37" s="2">
         <f t="shared" si="1"/>
         <v>77.699781609386719</v>
       </c>
@@ -6917,7 +6911,7 @@
       </c>
       <c r="V37" s="4">
         <f t="shared" si="1"/>
-        <v>79.802264961943052</v>
+        <v>79.818525124544678</v>
       </c>
     </row>
     <row r="38" spans="1:22">
@@ -6970,7 +6964,7 @@
       </c>
       <c r="M38" s="25">
         <f t="shared" si="2"/>
-        <v>7.0333333333333332</v>
+        <v>7.1</v>
       </c>
       <c r="N38" s="5">
         <f t="shared" si="2"/>
@@ -7006,7 +7000,7 @@
       </c>
       <c r="V38" s="6">
         <f t="shared" si="2"/>
-        <v>5.3666666666666663</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="39" spans="1:22">
@@ -7235,7 +7229,7 @@
         <f t="shared" si="5"/>
         <v>21</v>
       </c>
-      <c r="M41" s="28">
+      <c r="M41" s="7">
         <f t="shared" si="5"/>
         <v>24</v>
       </c>
@@ -7326,7 +7320,7 @@
       </c>
       <c r="M42" cm="1">
         <f t="array" ref="M42">SUM(--(M6:M35&lt;=$V6:$V35))</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N42" cm="1">
         <f t="array" ref="N42">SUM(--(N6:N35&lt;=$V6:$V35))</f>
@@ -7354,7 +7348,7 @@
       </c>
       <c r="T42" cm="1">
         <f t="array" ref="T42">SUM(--(T6:T35&lt;=$V6:$V35))</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="U42" cm="1">
         <f t="array" ref="U42">SUM(--(U6:U35&lt;=$V6:$V35))</f>
@@ -7483,10 +7477,10 @@
         <v>1.1389955577E-3</v>
       </c>
       <c r="L44" s="15">
-        <v>3.97302551879E-2</v>
+        <v>2.9000000000000001E-2</v>
       </c>
       <c r="M44" s="15">
-        <v>6.5308029432000004E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="N44" s="15">
         <v>8.4948726E-5</v>
@@ -7495,7 +7489,7 @@
         <v>1.0429514660000001E-4</v>
       </c>
       <c r="P44" s="15">
-        <v>5.8827127747000003E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="Q44" s="15">
         <v>4.8768206830000001E-4</v>
@@ -7507,10 +7501,10 @@
         <v>1.750380135E-4</v>
       </c>
       <c r="T44" s="15">
-        <v>3.2784897078099999E-2</v>
+        <v>2.5999999999999999E-2</v>
       </c>
       <c r="U44" s="15">
-        <v>4.1326511634099998E-2</v>
+        <v>3.9E-2</v>
       </c>
       <c r="V44" s="15">
         <v>1</v>
@@ -7837,43 +7831,43 @@
       </c>
       <c r="M53">
         <f t="shared" si="8"/>
+        <v>4</v>
+      </c>
+      <c r="N53">
+        <f t="shared" si="8"/>
+        <v>12</v>
+      </c>
+      <c r="O53">
+        <f t="shared" si="8"/>
+        <v>9</v>
+      </c>
+      <c r="P53">
+        <f t="shared" si="8"/>
+        <v>6</v>
+      </c>
+      <c r="Q53">
+        <f t="shared" si="8"/>
+        <v>20</v>
+      </c>
+      <c r="R53">
+        <f t="shared" si="8"/>
+        <v>6</v>
+      </c>
+      <c r="S53">
+        <f t="shared" si="8"/>
+        <v>12</v>
+      </c>
+      <c r="T53">
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
-      <c r="N53">
-        <f t="shared" si="8"/>
-        <v>12</v>
-      </c>
-      <c r="O53">
+      <c r="U53">
         <f t="shared" si="8"/>
         <v>9</v>
       </c>
-      <c r="P53">
-        <f t="shared" si="8"/>
-        <v>6</v>
-      </c>
-      <c r="Q53">
-        <f t="shared" si="8"/>
-        <v>20</v>
-      </c>
-      <c r="R53">
-        <f t="shared" si="8"/>
-        <v>6</v>
-      </c>
-      <c r="S53">
-        <f t="shared" si="8"/>
-        <v>12</v>
-      </c>
-      <c r="T53">
+      <c r="V53">
         <f t="shared" si="8"/>
         <v>2</v>
-      </c>
-      <c r="U53">
-        <f t="shared" si="8"/>
-        <v>9</v>
-      </c>
-      <c r="V53">
-        <f t="shared" si="8"/>
-        <v>4</v>
       </c>
     </row>
     <row r="54" spans="1:22">
@@ -10479,7 +10473,7 @@
       </c>
       <c r="U82">
         <f t="shared" si="13"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V82">
         <f>RANK(V38,$B38:$V38,1)</f>
@@ -11745,41 +11739,41 @@
   </cols>
   <sheetData>
     <row r="4" spans="1:22" ht="43" customHeight="1">
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26" t="s">
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="H4" s="26"/>
-      <c r="I4" s="26"/>
-      <c r="J4" s="26" t="s">
+      <c r="H4" s="27"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="K4" s="26"/>
-      <c r="L4" s="27" t="s">
+      <c r="K4" s="27"/>
+      <c r="L4" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="M4" s="27"/>
-      <c r="N4" s="26" t="s">
+      <c r="M4" s="28"/>
+      <c r="N4" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="O4" s="26"/>
-      <c r="P4" s="26"/>
-      <c r="Q4" s="26"/>
-      <c r="R4" s="26"/>
-      <c r="S4" s="26"/>
+      <c r="O4" s="27"/>
+      <c r="P4" s="27"/>
+      <c r="Q4" s="27"/>
+      <c r="R4" s="27"/>
+      <c r="S4" s="27"/>
       <c r="T4" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="U4" s="26" t="s">
+      <c r="U4" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="V4" s="26"/>
+      <c r="V4" s="27"/>
     </row>
     <row r="5" spans="1:22" ht="45">
       <c r="A5" t="s">
@@ -12194,7 +12188,7 @@
       </c>
       <c r="T9" s="3">
         <f>'UEA30 (colored)'!T9</f>
-        <v>80.487804878048792</v>
+        <v>80.487804878048806</v>
       </c>
       <c r="U9" s="2">
         <f>'UEA30 (colored)'!U9</f>
@@ -12202,7 +12196,7 @@
       </c>
       <c r="V9" s="2">
         <f>'UEA30 (colored)'!V9</f>
-        <v>80</v>
+        <v>80.487804878048806</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -14605,7 +14599,7 @@
       </c>
       <c r="V36" s="4">
         <f>'UEA30 (colored)'!V36</f>
-        <v>78.778660895649992</v>
+        <v>78.827441383454868</v>
       </c>
     </row>
     <row r="37" spans="1:22">
@@ -14684,7 +14678,7 @@
         <f>'UEA30 (colored)'!S37</f>
         <v>74.797352581492476</v>
       </c>
-      <c r="T37" s="29">
+      <c r="T37" s="2">
         <f>'UEA30 (colored)'!T37</f>
         <v>77.699781609386719</v>
       </c>
@@ -14694,7 +14688,7 @@
       </c>
       <c r="V37" s="4">
         <f>'UEA30 (colored)'!V37</f>
-        <v>79.802264961943052</v>
+        <v>79.818525124544678</v>
       </c>
     </row>
     <row r="38" spans="1:22">
@@ -14747,7 +14741,7 @@
       </c>
       <c r="M38" s="25">
         <f>'UEA30 (colored)'!M38</f>
-        <v>7.0333333333333332</v>
+        <v>7.1</v>
       </c>
       <c r="N38" s="5">
         <f>'UEA30 (colored)'!N38</f>
@@ -14783,7 +14777,7 @@
       </c>
       <c r="V38" s="6">
         <f>'UEA30 (colored)'!V38</f>
-        <v>5.3666666666666663</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="39" spans="1:22">
@@ -15012,7 +15006,7 @@
         <f>'UEA30 (colored)'!L41</f>
         <v>21</v>
       </c>
-      <c r="M41" s="28">
+      <c r="M41" s="7">
         <f>'UEA30 (colored)'!M41</f>
         <v>24</v>
       </c>
@@ -15103,7 +15097,7 @@
       </c>
       <c r="M42" s="7">
         <f>'UEA30 (colored)'!M42</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N42" s="7">
         <f>'UEA30 (colored)'!N42</f>
@@ -15131,7 +15125,7 @@
       </c>
       <c r="T42" s="7">
         <f>'UEA30 (colored)'!T42</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="U42" s="7">
         <f>'UEA30 (colored)'!U42</f>
@@ -15277,11 +15271,11 @@
       </c>
       <c r="L44" s="15">
         <f>'UEA30 (colored)'!L44</f>
-        <v>3.97302551879E-2</v>
+        <v>2.9000000000000001E-2</v>
       </c>
       <c r="M44" s="15">
         <f>'UEA30 (colored)'!M44</f>
-        <v>6.5308029432000004E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="N44" s="15">
         <f>'UEA30 (colored)'!N44</f>
@@ -15293,7 +15287,7 @@
       </c>
       <c r="P44" s="15">
         <f>'UEA30 (colored)'!P44</f>
-        <v>5.8827127747000003E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="Q44" s="15">
         <f>'UEA30 (colored)'!Q44</f>
@@ -15309,11 +15303,11 @@
       </c>
       <c r="T44" s="15">
         <f>'UEA30 (colored)'!T44</f>
-        <v>3.2784897078099999E-2</v>
+        <v>2.5999999999999999E-2</v>
       </c>
       <c r="U44" s="15">
         <f>'UEA30 (colored)'!U44</f>
-        <v>4.1326511634099998E-2</v>
+        <v>3.9E-2</v>
       </c>
       <c r="V44" s="15">
         <f>'UEA30 (colored)'!V44</f>
@@ -15641,43 +15635,43 @@
       </c>
       <c r="M53">
         <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="N53">
+        <f t="shared" si="4"/>
+        <v>12</v>
+      </c>
+      <c r="O53">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="P53">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="Q53">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="R53">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="S53">
+        <f t="shared" si="4"/>
+        <v>12</v>
+      </c>
+      <c r="T53">
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="N53">
-        <f t="shared" si="4"/>
-        <v>12</v>
-      </c>
-      <c r="O53">
+      <c r="U53">
         <f t="shared" si="4"/>
         <v>9</v>
       </c>
-      <c r="P53">
-        <f t="shared" si="4"/>
-        <v>6</v>
-      </c>
-      <c r="Q53">
-        <f t="shared" si="4"/>
-        <v>20</v>
-      </c>
-      <c r="R53">
-        <f t="shared" si="4"/>
-        <v>6</v>
-      </c>
-      <c r="S53">
-        <f t="shared" si="4"/>
-        <v>12</v>
-      </c>
-      <c r="T53">
+      <c r="V53">
         <f t="shared" si="4"/>
         <v>2</v>
-      </c>
-      <c r="U53">
-        <f t="shared" si="4"/>
-        <v>9</v>
-      </c>
-      <c r="V53">
-        <f t="shared" si="4"/>
-        <v>4</v>
       </c>
     </row>
     <row r="54" spans="1:22">
@@ -18283,7 +18277,7 @@
       </c>
       <c r="U82">
         <f t="shared" si="33"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V82">
         <f>RANK(V38,$B38:$V38,1)</f>
@@ -19156,41 +19150,41 @@
   </cols>
   <sheetData>
     <row r="4" spans="1:22" ht="43" customHeight="1">
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26" t="s">
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="H4" s="26"/>
-      <c r="I4" s="26"/>
-      <c r="J4" s="26" t="s">
+      <c r="H4" s="27"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="K4" s="26"/>
-      <c r="L4" s="27" t="s">
+      <c r="K4" s="27"/>
+      <c r="L4" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="M4" s="27"/>
-      <c r="N4" s="26" t="s">
+      <c r="M4" s="28"/>
+      <c r="N4" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="O4" s="26"/>
-      <c r="P4" s="26"/>
-      <c r="Q4" s="26"/>
-      <c r="R4" s="26"/>
-      <c r="S4" s="26"/>
+      <c r="O4" s="27"/>
+      <c r="P4" s="27"/>
+      <c r="Q4" s="27"/>
+      <c r="R4" s="27"/>
+      <c r="S4" s="27"/>
       <c r="T4" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="U4" s="26" t="s">
+      <c r="U4" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="V4" s="26"/>
+      <c r="V4" s="27"/>
     </row>
     <row r="5" spans="1:22" ht="45">
       <c r="A5" t="s">
@@ -19605,7 +19599,7 @@
       </c>
       <c r="T9" s="3">
         <f>'UEA30 (colored)'!T9</f>
-        <v>80.487804878048792</v>
+        <v>80.487804878048806</v>
       </c>
       <c r="U9" s="2">
         <f>'UEA30 (colored)'!U9</f>
@@ -19613,7 +19607,7 @@
       </c>
       <c r="V9" s="2">
         <f>'UEA30 (colored)'!V9</f>
-        <v>80</v>
+        <v>80.487804878048806</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -22016,7 +22010,7 @@
       </c>
       <c r="V36" s="4">
         <f>'UEA30 (colored)'!V36</f>
-        <v>78.778660895649992</v>
+        <v>78.827441383454868</v>
       </c>
     </row>
     <row r="37" spans="1:22">
@@ -22095,7 +22089,7 @@
         <f>'UEA30 (colored)'!S37</f>
         <v>74.797352581492476</v>
       </c>
-      <c r="T37" s="29">
+      <c r="T37" s="2">
         <f>'UEA30 (colored)'!T37</f>
         <v>77.699781609386719</v>
       </c>
@@ -22105,7 +22099,7 @@
       </c>
       <c r="V37" s="4">
         <f>'UEA30 (colored)'!V37</f>
-        <v>79.802264961943052</v>
+        <v>79.818525124544678</v>
       </c>
     </row>
     <row r="38" spans="1:22">
@@ -22158,7 +22152,7 @@
       </c>
       <c r="M38" s="25">
         <f>'UEA30 (colored)'!M38</f>
-        <v>7.0333333333333332</v>
+        <v>7.1</v>
       </c>
       <c r="N38" s="5">
         <f>'UEA30 (colored)'!N38</f>
@@ -22194,7 +22188,7 @@
       </c>
       <c r="V38" s="6">
         <f>'UEA30 (colored)'!V38</f>
-        <v>5.3666666666666663</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="39" spans="1:22">
@@ -22423,7 +22417,7 @@
         <f>'UEA30 (colored)'!L41</f>
         <v>21</v>
       </c>
-      <c r="M41" s="28">
+      <c r="M41" s="7">
         <f>'UEA30 (colored)'!M41</f>
         <v>24</v>
       </c>
@@ -22514,7 +22508,7 @@
       </c>
       <c r="M42" s="7">
         <f>'UEA30 (colored)'!M42</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N42" s="7">
         <f>'UEA30 (colored)'!N42</f>
@@ -22542,7 +22536,7 @@
       </c>
       <c r="T42" s="7">
         <f>'UEA30 (colored)'!T42</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="U42" s="7">
         <f>'UEA30 (colored)'!U42</f>
@@ -22688,11 +22682,11 @@
       </c>
       <c r="L44" s="15">
         <f>'UEA30 (colored)'!L44</f>
-        <v>3.97302551879E-2</v>
+        <v>2.9000000000000001E-2</v>
       </c>
       <c r="M44" s="15">
         <f>'UEA30 (colored)'!M44</f>
-        <v>6.5308029432000004E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="N44" s="15">
         <f>'UEA30 (colored)'!N44</f>
@@ -22704,7 +22698,7 @@
       </c>
       <c r="P44" s="15">
         <f>'UEA30 (colored)'!P44</f>
-        <v>5.8827127747000003E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="Q44" s="15">
         <f>'UEA30 (colored)'!Q44</f>
@@ -22720,11 +22714,11 @@
       </c>
       <c r="T44" s="15">
         <f>'UEA30 (colored)'!T44</f>
-        <v>3.2784897078099999E-2</v>
+        <v>2.5999999999999999E-2</v>
       </c>
       <c r="U44" s="15">
         <f>'UEA30 (colored)'!U44</f>
-        <v>4.1326511634099998E-2</v>
+        <v>3.9E-2</v>
       </c>
       <c r="V44" s="15"/>
     </row>
@@ -23049,43 +23043,43 @@
       </c>
       <c r="M53">
         <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="N53">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="O53">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="P53">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="Q53">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="R53">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="S53">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="T53">
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="N53">
-        <f t="shared" si="2"/>
-        <v>12</v>
-      </c>
-      <c r="O53">
+      <c r="U53">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
-      <c r="P53">
-        <f t="shared" si="2"/>
-        <v>6</v>
-      </c>
-      <c r="Q53">
-        <f t="shared" si="2"/>
-        <v>20</v>
-      </c>
-      <c r="R53">
-        <f t="shared" si="2"/>
-        <v>6</v>
-      </c>
-      <c r="S53">
-        <f t="shared" si="2"/>
-        <v>12</v>
-      </c>
-      <c r="T53">
+      <c r="V53">
         <f t="shared" si="2"/>
         <v>2</v>
-      </c>
-      <c r="U53">
-        <f t="shared" si="2"/>
-        <v>9</v>
-      </c>
-      <c r="V53">
-        <f t="shared" si="2"/>
-        <v>4</v>
       </c>
     </row>
     <row r="54" spans="1:22">
@@ -25691,7 +25685,7 @@
       </c>
       <c r="U82">
         <f t="shared" si="7"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V82">
         <f>RANK(V38,$B38:$V38,1)</f>
